--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935446</v>
+        <v>119935520</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
+        <v>90562</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553835</v>
+        <v>553815</v>
       </c>
       <c r="R2" t="n">
-        <v>6634247</v>
+        <v>6634221</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -943,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935597</v>
+        <v>119935446</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,38 +949,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -994,10 +986,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553806</v>
+        <v>553835</v>
       </c>
       <c r="R4" t="n">
-        <v>6634217</v>
+        <v>6634247</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1077,10 +1069,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935520</v>
+        <v>119935357</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1089,41 +1081,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553815</v>
+        <v>553761</v>
       </c>
       <c r="R5" t="n">
-        <v>6634221</v>
+        <v>6634190</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1203,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935357</v>
+        <v>119935492</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,51 +1217,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553761</v>
+        <v>553819</v>
       </c>
       <c r="R6" t="n">
-        <v>6634190</v>
+        <v>6634249</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1339,10 +1331,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935427</v>
+        <v>119935597</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,36 +1343,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1388,10 +1382,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553848</v>
+        <v>553806</v>
       </c>
       <c r="R7" t="n">
-        <v>6634240</v>
+        <v>6634217</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1471,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935492</v>
+        <v>119935427</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,30 +1477,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553819</v>
+        <v>553848</v>
       </c>
       <c r="R8" t="n">
-        <v>6634249</v>
+        <v>6634240</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1719,6 +1719,1662 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120157172</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>553747</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6634278</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120157354</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>553723</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6634334</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120163608</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lefelingen, Lefelingen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>553722</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6634626</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120156999</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>553742</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6634218</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120169031</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>553676</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6634439</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120158850</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>553726</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6634313</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120156648</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>553796</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6634191</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120159215</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>553741</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6634339</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120168703</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105009</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>553705</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6634586</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120169088</v>
+      </c>
+      <c r="B19" t="n">
+        <v>95455</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>53</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>553723</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6634334</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120164833</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lefelingen, Lefelingen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>553695</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6634564</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120168936</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>553676</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6634439</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120156618</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>553801</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6634191</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935520</v>
+        <v>119931736</v>
       </c>
       <c r="B2" t="n">
         <v>90562</v>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553815</v>
+        <v>553816</v>
       </c>
       <c r="R2" t="n">
-        <v>6634221</v>
+        <v>6634237</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,9 +751,19 @@
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,14 +804,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119931736</v>
+        <v>119935597</v>
       </c>
       <c r="B3" t="n">
         <v>90562</v>
@@ -834,8 +844,16 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -844,13 +862,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553816</v>
+        <v>553806</v>
       </c>
       <c r="R3" t="n">
-        <v>6634237</v>
+        <v>6634217</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,19 +895,9 @@
           <t>2024-09-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,17 +938,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935446</v>
+        <v>119935492</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>90562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,36 +957,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -986,10 +988,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553835</v>
+        <v>553819</v>
       </c>
       <c r="R4" t="n">
-        <v>6634247</v>
+        <v>6634249</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1069,7 +1071,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935357</v>
+        <v>119935427</v>
       </c>
       <c r="B5" t="n">
         <v>5169</v>
@@ -1111,21 +1113,17 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553761</v>
+        <v>553848</v>
       </c>
       <c r="R5" t="n">
-        <v>6634190</v>
+        <v>6634240</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1205,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935492</v>
+        <v>119935446</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,30 +1215,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1248,10 +1252,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553819</v>
+        <v>553835</v>
       </c>
       <c r="R6" t="n">
-        <v>6634249</v>
+        <v>6634247</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1331,7 +1335,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935597</v>
+        <v>119935520</v>
       </c>
       <c r="B7" t="n">
         <v>90562</v>
@@ -1364,16 +1368,8 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1382,10 +1378,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553806</v>
+        <v>553815</v>
       </c>
       <c r="R7" t="n">
-        <v>6634217</v>
+        <v>6634221</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1465,7 +1461,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935427</v>
+        <v>119935357</v>
       </c>
       <c r="B8" t="n">
         <v>5169</v>
@@ -1507,17 +1503,21 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553848</v>
+        <v>553761</v>
       </c>
       <c r="R8" t="n">
-        <v>6634240</v>
+        <v>6634190</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120157172</v>
+        <v>120156618</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1737,49 +1737,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553747</v>
+        <v>553801</v>
       </c>
       <c r="R10" t="n">
-        <v>6634278</v>
+        <v>6634191</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1808,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1818,7 +1814,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1832,28 +1833,28 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120157354</v>
+        <v>120163608</v>
       </c>
       <c r="B11" t="n">
-        <v>8432</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,50 +1863,57 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553723</v>
+        <v>553722</v>
       </c>
       <c r="R11" t="n">
-        <v>6634334</v>
+        <v>6634626</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1934,7 +1942,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1944,7 +1952,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1959,28 +1967,28 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120163608</v>
+        <v>120157354</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1989,57 +1997,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553722</v>
+        <v>553723</v>
       </c>
       <c r="R12" t="n">
-        <v>6634626</v>
+        <v>6634334</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2068,7 +2069,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2078,7 +2079,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2093,25 +2094,25 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120156999</v>
+        <v>120157172</v>
       </c>
       <c r="B13" t="n">
         <v>57463</v>
@@ -2163,13 +2164,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553742</v>
+        <v>553747</v>
       </c>
       <c r="R13" t="n">
-        <v>6634218</v>
+        <v>6634278</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2198,7 +2199,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2208,7 +2209,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2240,10 +2241,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120169031</v>
+        <v>120164833</v>
       </c>
       <c r="B14" t="n">
-        <v>90527</v>
+        <v>57463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2252,44 +2253,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553676</v>
+        <v>553695</v>
       </c>
       <c r="R14" t="n">
-        <v>6634439</v>
+        <v>6634564</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2316,60 +2326,54 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120158850</v>
+        <v>120156648</v>
       </c>
       <c r="B15" t="n">
-        <v>90527</v>
+        <v>57326</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2378,38 +2382,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2417,13 +2422,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553726</v>
+        <v>553796</v>
       </c>
       <c r="R15" t="n">
-        <v>6634313</v>
+        <v>6634191</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2452,7 +2457,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2462,7 +2467,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2471,7 +2476,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2488,17 +2492,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120156648</v>
+        <v>120169088</v>
       </c>
       <c r="B16" t="n">
-        <v>57326</v>
+        <v>95455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2511,46 +2515,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553796</v>
+        <v>553723</v>
       </c>
       <c r="R16" t="n">
-        <v>6634191</v>
+        <v>6634334</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2580,44 +2584,35 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2753,10 +2748,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168703</v>
+        <v>120158850</v>
       </c>
       <c r="B18" t="n">
-        <v>105009</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2769,54 +2764,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553705</v>
+        <v>553726</v>
       </c>
       <c r="R18" t="n">
-        <v>6634586</v>
+        <v>6634313</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2846,9 +2832,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2863,28 +2859,28 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120169088</v>
+        <v>120168936</v>
       </c>
       <c r="B19" t="n">
-        <v>95455</v>
+        <v>8432</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2893,39 +2889,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2933,10 +2926,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553723</v>
+        <v>553676</v>
       </c>
       <c r="R19" t="n">
-        <v>6634334</v>
+        <v>6634439</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2994,17 +2987,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120164833</v>
+        <v>120169031</v>
       </c>
       <c r="B20" t="n">
-        <v>57463</v>
+        <v>90527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3013,53 +3006,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553695</v>
+        <v>553676</v>
       </c>
       <c r="R20" t="n">
-        <v>6634564</v>
+        <v>6634439</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3086,54 +3070,60 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168936</v>
+        <v>120168703</v>
       </c>
       <c r="B21" t="n">
-        <v>8432</v>
+        <v>105009</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3146,46 +3136,57 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553676</v>
+        <v>553705</v>
       </c>
       <c r="R21" t="n">
-        <v>6634439</v>
+        <v>6634586</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3240,17 +3241,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120156618</v>
+        <v>120156999</v>
       </c>
       <c r="B22" t="n">
-        <v>57326</v>
+        <v>57463</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3263,45 +3264,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553801</v>
+        <v>553742</v>
       </c>
       <c r="R22" t="n">
-        <v>6634191</v>
+        <v>6634218</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3330,7 +3335,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3340,12 +3345,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska spår av födosök på gran</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3359,18 +3359,18 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119935336</v>
+        <v>120156618</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1609,57 +1609,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553767</v>
+        <v>553801</v>
       </c>
       <c r="R9" t="n">
-        <v>6634197</v>
+        <v>6634191</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1683,12 +1675,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,7 +1704,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1721,10 +1727,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120156618</v>
+        <v>120163608</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1733,49 +1739,57 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553801</v>
+        <v>553722</v>
       </c>
       <c r="R10" t="n">
-        <v>6634191</v>
+        <v>6634626</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1804,7 +1818,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,12 +1828,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska spår av födosök på gran</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1828,33 +1837,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120163608</v>
+        <v>120157354</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1863,57 +1873,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553722</v>
+        <v>553723</v>
       </c>
       <c r="R11" t="n">
-        <v>6634626</v>
+        <v>6634334</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1942,7 +1945,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1952,7 +1955,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1967,28 +1970,28 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120157354</v>
+        <v>120157172</v>
       </c>
       <c r="B12" t="n">
-        <v>8432</v>
+        <v>57463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1997,50 +2000,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553723</v>
+        <v>553747</v>
       </c>
       <c r="R12" t="n">
-        <v>6634334</v>
+        <v>6634278</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2069,7 +2075,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2079,7 +2085,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2088,31 +2094,30 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120157172</v>
+        <v>120164833</v>
       </c>
       <c r="B13" t="n">
         <v>57463</v>
@@ -2160,14 +2165,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553747</v>
+        <v>553695</v>
       </c>
       <c r="R13" t="n">
-        <v>6634278</v>
+        <v>6634564</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2199,7 +2204,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2209,7 +2214,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2234,17 +2239,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120164833</v>
+        <v>120156648</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>57326</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2257,21 +2262,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2283,23 +2288,23 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553695</v>
+        <v>553796</v>
       </c>
       <c r="R14" t="n">
-        <v>6634564</v>
+        <v>6634191</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2328,7 +2333,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2338,7 +2343,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2363,17 +2368,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120156648</v>
+        <v>120169088</v>
       </c>
       <c r="B15" t="n">
-        <v>57326</v>
+        <v>95455</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2386,46 +2391,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553796</v>
+        <v>553723</v>
       </c>
       <c r="R15" t="n">
-        <v>6634191</v>
+        <v>6634334</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2455,54 +2460,45 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120169088</v>
+        <v>120159215</v>
       </c>
       <c r="B16" t="n">
-        <v>95455</v>
+        <v>90527</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2511,25 +2507,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2543,21 +2539,20 @@
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553723</v>
+        <v>553741</v>
       </c>
       <c r="R16" t="n">
-        <v>6634334</v>
+        <v>6634339</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2584,9 +2579,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2601,25 +2606,25 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120159215</v>
+        <v>120158850</v>
       </c>
       <c r="B17" t="n">
         <v>90527</v>
@@ -2670,10 +2675,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553741</v>
+        <v>553726</v>
       </c>
       <c r="R17" t="n">
-        <v>6634339</v>
+        <v>6634313</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2705,7 +2710,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2715,7 +2720,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2748,10 +2753,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120158850</v>
+        <v>120156999</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>57463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2760,38 +2765,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2799,13 +2805,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553726</v>
+        <v>553742</v>
       </c>
       <c r="R18" t="n">
-        <v>6634313</v>
+        <v>6634218</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2834,7 +2840,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2844,7 +2850,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2853,7 +2859,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2870,7 +2875,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3120,10 +3125,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168703</v>
+        <v>119935336</v>
       </c>
       <c r="B21" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3132,30 +3137,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3165,28 +3170,24 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553705</v>
+        <v>553767</v>
       </c>
       <c r="R21" t="n">
-        <v>6634586</v>
+        <v>6634197</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3210,12 +3211,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3241,17 +3242,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120156999</v>
+        <v>120168703</v>
       </c>
       <c r="B22" t="n">
-        <v>57463</v>
+        <v>105009</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3260,25 +3261,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3286,27 +3287,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553742</v>
+        <v>553705</v>
       </c>
       <c r="R22" t="n">
-        <v>6634218</v>
+        <v>6634586</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3333,47 +3342,312 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120156458</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>553814</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6634170</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120193653</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lefelingen, Virsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>553699</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6634610</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -811,7 +811,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119935597</v>
+        <v>119935492</v>
       </c>
       <c r="B3" t="n">
         <v>90562</v>
@@ -844,16 +844,8 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -862,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553806</v>
+        <v>553819</v>
       </c>
       <c r="R3" t="n">
-        <v>6634217</v>
+        <v>6634249</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -945,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935492</v>
+        <v>119935357</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,41 +949,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553819</v>
+        <v>553761</v>
       </c>
       <c r="R4" t="n">
-        <v>6634249</v>
+        <v>6634190</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1071,10 +1073,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935427</v>
+        <v>119935520</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,36 +1085,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1120,10 +1116,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553848</v>
+        <v>553815</v>
       </c>
       <c r="R5" t="n">
-        <v>6634240</v>
+        <v>6634221</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1203,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935446</v>
+        <v>119935427</v>
       </c>
       <c r="B6" t="n">
         <v>5169</v>
@@ -1252,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553835</v>
+        <v>553848</v>
       </c>
       <c r="R6" t="n">
-        <v>6634247</v>
+        <v>6634240</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1335,10 +1331,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935520</v>
+        <v>119935446</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,30 +1343,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1378,10 +1380,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553815</v>
+        <v>553835</v>
       </c>
       <c r="R7" t="n">
-        <v>6634221</v>
+        <v>6634247</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1461,10 +1463,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935357</v>
+        <v>119935597</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
+        <v>90562</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1473,51 +1475,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553761</v>
+        <v>553806</v>
       </c>
       <c r="R8" t="n">
-        <v>6634190</v>
+        <v>6634217</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120163608</v>
+        <v>120156648</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1739,25 +1739,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1765,31 +1765,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553722</v>
+        <v>553796</v>
       </c>
       <c r="R10" t="n">
-        <v>6634626</v>
+        <v>6634191</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1818,7 +1814,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1828,7 +1824,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1837,7 +1833,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1854,17 +1849,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120157354</v>
+        <v>120158850</v>
       </c>
       <c r="B11" t="n">
-        <v>8432</v>
+        <v>90527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1877,46 +1872,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553723</v>
+        <v>553726</v>
       </c>
       <c r="R11" t="n">
-        <v>6634334</v>
+        <v>6634313</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1945,7 +1942,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1955,7 +1952,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1970,18 +1967,18 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2117,10 +2114,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120164833</v>
+        <v>120169088</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
+        <v>95455</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2133,49 +2130,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553695</v>
+        <v>553723</v>
       </c>
       <c r="R13" t="n">
-        <v>6634564</v>
+        <v>6634334</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2202,54 +2199,45 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120156648</v>
+        <v>120156999</v>
       </c>
       <c r="B14" t="n">
-        <v>57326</v>
+        <v>57463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2262,21 +2250,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2288,7 +2276,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2298,13 +2286,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553796</v>
+        <v>553742</v>
       </c>
       <c r="R14" t="n">
-        <v>6634191</v>
+        <v>6634218</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2333,7 +2321,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2343,7 +2331,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2375,10 +2363,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120169088</v>
+        <v>120164833</v>
       </c>
       <c r="B15" t="n">
-        <v>95455</v>
+        <v>57463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2391,49 +2379,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553723</v>
+        <v>553695</v>
       </c>
       <c r="R15" t="n">
-        <v>6634334</v>
+        <v>6634564</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2460,45 +2448,54 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120159215</v>
+        <v>120168936</v>
       </c>
       <c r="B16" t="n">
-        <v>90527</v>
+        <v>8432</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2511,48 +2508,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553741</v>
+        <v>553676</v>
       </c>
       <c r="R16" t="n">
-        <v>6634339</v>
+        <v>6634439</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2579,19 +2574,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2606,28 +2591,28 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120158850</v>
+        <v>120163608</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2636,49 +2621,54 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553726</v>
+        <v>553722</v>
       </c>
       <c r="R17" t="n">
-        <v>6634313</v>
+        <v>6634626</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2710,7 +2700,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2720,7 +2710,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,17 +2736,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120156999</v>
+        <v>120159215</v>
       </c>
       <c r="B18" t="n">
-        <v>57463</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2765,39 +2755,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2805,13 +2794,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553742</v>
+        <v>553741</v>
       </c>
       <c r="R18" t="n">
-        <v>6634218</v>
+        <v>6634339</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2840,7 +2829,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2850,7 +2839,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2859,6 +2848,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2875,14 +2865,14 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168936</v>
+        <v>120157354</v>
       </c>
       <c r="B19" t="n">
         <v>8432</v>
@@ -2931,10 +2921,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553676</v>
+        <v>553723</v>
       </c>
       <c r="R19" t="n">
-        <v>6634439</v>
+        <v>6634334</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2964,9 +2954,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3125,7 +3125,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119935336</v>
+        <v>120193653</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3174,20 +3174,24 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lefelingen, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553767</v>
+        <v>553699</v>
       </c>
       <c r="R21" t="n">
-        <v>6634197</v>
+        <v>6634610</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3211,12 +3215,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3242,7 +3256,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3513,7 +3527,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120193653</v>
+        <v>119935336</v>
       </c>
       <c r="B24" t="n">
         <v>97907</v>
@@ -3548,7 +3562,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3562,24 +3576,20 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lefelingen, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553699</v>
+        <v>553767</v>
       </c>
       <c r="R24" t="n">
-        <v>6634610</v>
+        <v>6634197</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3603,22 +3613,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3649,6 +3649,130 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120235206</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90334</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>553761</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6634402</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -2114,10 +2114,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120169088</v>
+        <v>120156999</v>
       </c>
       <c r="B13" t="n">
-        <v>95455</v>
+        <v>57463</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2130,49 +2130,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553723</v>
+        <v>553742</v>
       </c>
       <c r="R13" t="n">
-        <v>6634334</v>
+        <v>6634218</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2199,45 +2199,54 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120156999</v>
+        <v>120169088</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>95455</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2250,49 +2259,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553742</v>
+        <v>553723</v>
       </c>
       <c r="R14" t="n">
-        <v>6634218</v>
+        <v>6634334</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2319,44 +2328,35 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2114,10 +2114,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120156999</v>
+        <v>120169088</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
+        <v>95455</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2130,49 +2130,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553742</v>
+        <v>553723</v>
       </c>
       <c r="R13" t="n">
-        <v>6634218</v>
+        <v>6634334</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2199,54 +2199,45 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120169088</v>
+        <v>120156999</v>
       </c>
       <c r="B14" t="n">
-        <v>95455</v>
+        <v>57463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2259,49 +2250,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553723</v>
+        <v>553742</v>
       </c>
       <c r="R14" t="n">
-        <v>6634334</v>
+        <v>6634218</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2328,35 +2319,44 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3649,130 +3649,6 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>120235206</v>
-      </c>
-      <c r="B25" t="n">
-        <v>90334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>3215</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>553761</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6634402</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120156618</v>
+        <v>120158850</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>90527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1609,49 +1609,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553801</v>
+        <v>553726</v>
       </c>
       <c r="R9" t="n">
-        <v>6634191</v>
+        <v>6634313</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1680,7 +1683,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1690,12 +1693,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska spår av födosök på gran</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1704,33 +1702,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120156648</v>
+        <v>120169088</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>95455</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1743,46 +1742,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553796</v>
+        <v>553723</v>
       </c>
       <c r="R10" t="n">
-        <v>6634191</v>
+        <v>6634334</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1812,54 +1811,45 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120158850</v>
+        <v>120168936</v>
       </c>
       <c r="B11" t="n">
-        <v>90527</v>
+        <v>8432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,48 +1862,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553726</v>
+        <v>553676</v>
       </c>
       <c r="R11" t="n">
-        <v>6634313</v>
+        <v>6634439</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1940,19 +1928,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1967,28 +1945,28 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120157172</v>
+        <v>120163608</v>
       </c>
       <c r="B12" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1997,25 +1975,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2023,27 +2001,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553747</v>
+        <v>553722</v>
       </c>
       <c r="R12" t="n">
-        <v>6634278</v>
+        <v>6634626</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2072,7 +2054,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2082,7 +2064,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2091,6 +2073,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2107,17 +2090,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120169088</v>
+        <v>120159215</v>
       </c>
       <c r="B13" t="n">
-        <v>95455</v>
+        <v>90527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2126,25 +2109,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2158,21 +2141,20 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553723</v>
+        <v>553741</v>
       </c>
       <c r="R13" t="n">
-        <v>6634334</v>
+        <v>6634339</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2199,9 +2181,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2216,28 +2208,28 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120156999</v>
+        <v>120157354</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>8432</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2246,53 +2238,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553742</v>
+        <v>553723</v>
       </c>
       <c r="R14" t="n">
-        <v>6634218</v>
+        <v>6634334</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2321,7 +2310,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2331,7 +2320,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2340,33 +2329,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120164833</v>
+        <v>120169031</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>90527</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2375,53 +2365,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553695</v>
+        <v>553676</v>
       </c>
       <c r="R15" t="n">
-        <v>6634564</v>
+        <v>6634439</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2448,54 +2429,60 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168936</v>
+        <v>120193653</v>
       </c>
       <c r="B16" t="n">
-        <v>8432</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2504,50 +2491,61 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lefelingen, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553676</v>
+        <v>553699</v>
       </c>
       <c r="R16" t="n">
-        <v>6634439</v>
+        <v>6634610</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2574,9 +2572,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2609,10 +2617,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120163608</v>
+        <v>120168703</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2621,25 +2629,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2654,21 +2662,25 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553722</v>
+        <v>553705</v>
       </c>
       <c r="R17" t="n">
-        <v>6634626</v>
+        <v>6634586</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2698,19 +2710,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2725,28 +2727,28 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120159215</v>
+        <v>120156458</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>5169</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2759,48 +2761,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553741</v>
+        <v>553814</v>
       </c>
       <c r="R18" t="n">
-        <v>6634339</v>
+        <v>6634170</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2829,7 +2833,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2839,7 +2843,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2854,28 +2863,28 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120157354</v>
+        <v>119935336</v>
       </c>
       <c r="B19" t="n">
-        <v>8432</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2884,50 +2893,57 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553723</v>
+        <v>553767</v>
       </c>
       <c r="R19" t="n">
-        <v>6634334</v>
+        <v>6634197</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2951,22 +2967,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2999,56 +3005,65 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120169031</v>
+        <v>120157172</v>
       </c>
       <c r="B20" t="n">
-        <v>90527</v>
+        <v>57463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553676</v>
+        <v>553747</v>
       </c>
       <c r="R20" t="n">
-        <v>6634439</v>
+        <v>6634278</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3075,87 +3090,81 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120193653</v>
+        <v>120156648</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3163,35 +3172,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lefelingen, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553699</v>
+        <v>553796</v>
       </c>
       <c r="R21" t="n">
-        <v>6634610</v>
+        <v>6634191</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3220,7 +3221,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3230,7 +3231,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3239,97 +3240,84 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168703</v>
+        <v>120156618</v>
       </c>
       <c r="B22" t="n">
-        <v>105009</v>
+        <v>57326</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553705</v>
+        <v>553801</v>
       </c>
       <c r="R22" t="n">
-        <v>6634586</v>
+        <v>6634191</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3356,18 +3344,32 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på gran</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3384,73 +3386,72 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120156458</v>
+        <v>120156999</v>
       </c>
       <c r="B23" t="n">
-        <v>5169</v>
+        <v>57463</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>553814</v>
+        <v>553742</v>
       </c>
       <c r="R23" t="n">
-        <v>6634170</v>
+        <v>6634218</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3479,7 +3480,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3489,12 +3490,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3503,90 +3499,85 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119935336</v>
+        <v>120164833</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553767</v>
+        <v>553695</v>
       </c>
       <c r="R24" t="n">
-        <v>6634197</v>
+        <v>6634564</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3613,12 +3604,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3627,24 +3628,23 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3649,6 +3649,125 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120319498</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90594</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tordyvelskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>553728</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6634325</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På grov granlåga</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119931736</v>
+        <v>119935597</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,8 +708,16 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553816</v>
+        <v>553806</v>
       </c>
       <c r="R2" t="n">
-        <v>6634237</v>
+        <v>6634217</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +759,9 @@
           <t>2024-09-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,17 +802,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119935492</v>
+        <v>119931736</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -854,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553819</v>
+        <v>553816</v>
       </c>
       <c r="R3" t="n">
-        <v>6634249</v>
+        <v>6634237</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,9 +885,19 @@
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,14 +938,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935357</v>
+        <v>119935427</v>
       </c>
       <c r="B4" t="n">
         <v>5169</v>
@@ -979,21 +987,17 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553761</v>
+        <v>553848</v>
       </c>
       <c r="R4" t="n">
-        <v>6634190</v>
+        <v>6634240</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1073,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935520</v>
+        <v>119935357</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,41 +1089,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553815</v>
+        <v>553761</v>
       </c>
       <c r="R5" t="n">
-        <v>6634221</v>
+        <v>6634190</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1199,10 +1213,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935427</v>
+        <v>119935492</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,36 +1225,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1248,10 +1256,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553848</v>
+        <v>553819</v>
       </c>
       <c r="R6" t="n">
-        <v>6634240</v>
+        <v>6634249</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1331,10 +1339,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935446</v>
+        <v>119935520</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1343,36 +1351,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1380,10 +1382,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553835</v>
+        <v>553815</v>
       </c>
       <c r="R7" t="n">
-        <v>6634247</v>
+        <v>6634221</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1463,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935597</v>
+        <v>119935446</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1475,38 +1477,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553806</v>
+        <v>553835</v>
       </c>
       <c r="R8" t="n">
-        <v>6634217</v>
+        <v>6634247</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120158850</v>
+        <v>120159215</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553726</v>
+        <v>553741</v>
       </c>
       <c r="R9" t="n">
-        <v>6634313</v>
+        <v>6634339</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Seppo Ormiskangas, Bengt Eriksson, Leif Tallberg, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120169088</v>
+        <v>120163608</v>
       </c>
       <c r="B10" t="n">
-        <v>95455</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1738,53 +1738,57 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553723</v>
+        <v>553722</v>
       </c>
       <c r="R10" t="n">
-        <v>6634334</v>
+        <v>6634626</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1811,9 +1815,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1828,28 +1842,28 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168936</v>
+        <v>120169031</v>
       </c>
       <c r="B11" t="n">
-        <v>8432</v>
+        <v>90545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,32 +1876,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1946,6 +1954,21 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1963,10 +1986,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120163608</v>
+        <v>120158850</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>90545</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1975,54 +1998,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553722</v>
+        <v>553726</v>
       </c>
       <c r="R12" t="n">
-        <v>6634626</v>
+        <v>6634313</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -2054,7 +2072,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2064,7 +2082,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2090,17 +2108,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120159215</v>
+        <v>120157354</v>
       </c>
       <c r="B13" t="n">
-        <v>90527</v>
+        <v>8432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2113,48 +2131,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553741</v>
+        <v>553723</v>
       </c>
       <c r="R13" t="n">
-        <v>6634339</v>
+        <v>6634334</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2183,7 +2199,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2193,7 +2209,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2208,28 +2224,28 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120157354</v>
+        <v>120169088</v>
       </c>
       <c r="B14" t="n">
-        <v>8432</v>
+        <v>95478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2238,36 +2254,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2308,19 +2327,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2346,17 +2355,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120169031</v>
+        <v>120168936</v>
       </c>
       <c r="B15" t="n">
-        <v>90527</v>
+        <v>8432</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2369,26 +2378,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2447,21 +2462,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120193653</v>
+        <v>120156458</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2491,43 +2491,36 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2535,17 +2528,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lefelingen, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553699</v>
+        <v>553814</v>
       </c>
       <c r="R16" t="n">
-        <v>6634610</v>
+        <v>6634170</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2574,7 +2567,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2584,7 +2577,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2610,7 +2608,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2620,7 +2618,7 @@
         <v>120168703</v>
       </c>
       <c r="B17" t="n">
-        <v>105009</v>
+        <v>105032</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2745,10 +2743,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120156458</v>
+        <v>120193653</v>
       </c>
       <c r="B18" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2757,36 +2755,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2794,17 +2799,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lefelingen, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553814</v>
+        <v>553699</v>
       </c>
       <c r="R18" t="n">
-        <v>6634170</v>
+        <v>6634610</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2833,7 +2838,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2843,12 +2848,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
         <v>119935336</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120157172</v>
+        <v>120164833</v>
       </c>
       <c r="B20" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3053,14 +3053,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553747</v>
+        <v>553695</v>
       </c>
       <c r="R20" t="n">
-        <v>6634278</v>
+        <v>6634564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
         <v>120156648</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>120156618</v>
       </c>
       <c r="B22" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120156999</v>
+        <v>120157172</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3445,13 +3445,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>553742</v>
+        <v>553747</v>
       </c>
       <c r="R23" t="n">
-        <v>6634218</v>
+        <v>6634278</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3522,10 +3522,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120164833</v>
+        <v>120156999</v>
       </c>
       <c r="B24" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3570,17 +3570,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553695</v>
+        <v>553742</v>
       </c>
       <c r="R24" t="n">
-        <v>6634564</v>
+        <v>6634218</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -2615,10 +2615,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168703</v>
+        <v>120193653</v>
       </c>
       <c r="B17" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2627,25 +2627,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2671,14 +2671,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lefelingen, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553705</v>
+        <v>553699</v>
       </c>
       <c r="R17" t="n">
-        <v>6634586</v>
+        <v>6634610</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2708,9 +2708,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2736,17 +2746,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120193653</v>
+        <v>120168703</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2755,25 +2765,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2788,7 +2798,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2799,14 +2809,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lefelingen, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553699</v>
+        <v>553705</v>
       </c>
       <c r="R18" t="n">
-        <v>6634610</v>
+        <v>6634586</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2836,19 +2846,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -945,7 +945,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935427</v>
+        <v>119935357</v>
       </c>
       <c r="B4" t="n">
         <v>5169</v>
@@ -987,17 +987,21 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553848</v>
+        <v>553761</v>
       </c>
       <c r="R4" t="n">
-        <v>6634240</v>
+        <v>6634190</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1077,7 +1081,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935357</v>
+        <v>119935427</v>
       </c>
       <c r="B5" t="n">
         <v>5169</v>
@@ -1119,21 +1123,17 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553761</v>
+        <v>553848</v>
       </c>
       <c r="R5" t="n">
-        <v>6634190</v>
+        <v>6634240</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935520</v>
+        <v>119935446</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,30 +1351,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1382,10 +1388,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553815</v>
+        <v>553835</v>
       </c>
       <c r="R7" t="n">
-        <v>6634221</v>
+        <v>6634247</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1465,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935446</v>
+        <v>119935520</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1477,36 +1483,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553835</v>
+        <v>553815</v>
       </c>
       <c r="R8" t="n">
-        <v>6634247</v>
+        <v>6634221</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120159215</v>
+        <v>120157354</v>
       </c>
       <c r="B9" t="n">
-        <v>90545</v>
+        <v>8432</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1613,48 +1613,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553741</v>
+        <v>553723</v>
       </c>
       <c r="R9" t="n">
-        <v>6634339</v>
+        <v>6634334</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1683,7 +1681,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1693,7 +1691,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1708,28 +1706,28 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Bengt Eriksson, Leif Tallberg, Sören Larsson, Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120163608</v>
+        <v>120168936</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>8432</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1738,57 +1736,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553722</v>
+        <v>553676</v>
       </c>
       <c r="R10" t="n">
-        <v>6634626</v>
+        <v>6634439</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1815,19 +1806,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1842,13 +1823,13 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1860,10 +1841,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120169031</v>
+        <v>120169088</v>
       </c>
       <c r="B11" t="n">
-        <v>90545</v>
+        <v>95478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,30 +1853,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1903,10 +1893,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553676</v>
+        <v>553723</v>
       </c>
       <c r="R11" t="n">
-        <v>6634439</v>
+        <v>6634334</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1956,21 +1946,6 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1979,7 +1954,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2115,10 +2090,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120157354</v>
+        <v>120159215</v>
       </c>
       <c r="B13" t="n">
-        <v>8432</v>
+        <v>90545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2131,46 +2106,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553723</v>
+        <v>553741</v>
       </c>
       <c r="R13" t="n">
-        <v>6634334</v>
+        <v>6634339</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2199,7 +2176,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2209,7 +2186,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2224,28 +2201,28 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120169088</v>
+        <v>120163608</v>
       </c>
       <c r="B14" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2254,53 +2231,57 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553723</v>
+        <v>553722</v>
       </c>
       <c r="R14" t="n">
-        <v>6634334</v>
+        <v>6634626</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2327,9 +2308,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2344,28 +2335,28 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168936</v>
+        <v>120169031</v>
       </c>
       <c r="B15" t="n">
-        <v>8432</v>
+        <v>90545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2378,32 +2369,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2462,6 +2447,21 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120164833</v>
+        <v>120156999</v>
       </c>
       <c r="B20" t="n">
         <v>57473</v>
@@ -3053,17 +3053,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553695</v>
+        <v>553742</v>
       </c>
       <c r="R20" t="n">
-        <v>6634564</v>
+        <v>6634218</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120156648</v>
+        <v>120156618</v>
       </c>
       <c r="B21" t="n">
         <v>57336</v>
@@ -3167,11 +3167,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
@@ -3182,11 +3178,11 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553796</v>
+        <v>553801</v>
       </c>
       <c r="R21" t="n">
         <v>6634191</v>
@@ -3221,7 +3217,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3231,7 +3227,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3245,28 +3246,28 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120156618</v>
+        <v>120164833</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3279,45 +3280,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553801</v>
+        <v>553695</v>
       </c>
       <c r="R22" t="n">
-        <v>6634191</v>
+        <v>6634564</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3346,7 +3351,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3356,12 +3361,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska spår av födosök på gran</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3375,28 +3375,28 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120157172</v>
+        <v>120156648</v>
       </c>
       <c r="B23" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3409,21 +3409,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3435,7 +3435,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3445,13 +3445,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>553747</v>
+        <v>553796</v>
       </c>
       <c r="R23" t="n">
-        <v>6634278</v>
+        <v>6634191</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3522,7 +3522,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120156999</v>
+        <v>120157172</v>
       </c>
       <c r="B24" t="n">
         <v>57473</v>
@@ -3574,13 +3574,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553742</v>
+        <v>553747</v>
       </c>
       <c r="R24" t="n">
-        <v>6634218</v>
+        <v>6634278</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935597</v>
+        <v>119935427</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553806</v>
+        <v>553848</v>
       </c>
       <c r="R2" t="n">
-        <v>6634217</v>
+        <v>6634240</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -809,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119931736</v>
+        <v>119935357</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,44 +819,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553816</v>
+        <v>553761</v>
       </c>
       <c r="R3" t="n">
-        <v>6634237</v>
+        <v>6634190</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,19 +893,9 @@
           <t>2024-09-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,17 +936,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935357</v>
+        <v>119935492</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,51 +955,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553761</v>
+        <v>553819</v>
       </c>
       <c r="R4" t="n">
-        <v>6634190</v>
+        <v>6634249</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1081,10 +1069,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935427</v>
+        <v>119931736</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1093,36 +1081,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1130,13 +1112,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553848</v>
+        <v>553816</v>
       </c>
       <c r="R5" t="n">
-        <v>6634240</v>
+        <v>6634237</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1163,9 +1145,19 @@
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1206,14 +1198,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935492</v>
+        <v>119935520</v>
       </c>
       <c r="B6" t="n">
         <v>90580</v>
@@ -1256,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553819</v>
+        <v>553815</v>
       </c>
       <c r="R6" t="n">
-        <v>6634249</v>
+        <v>6634221</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1471,7 +1463,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935520</v>
+        <v>119935597</v>
       </c>
       <c r="B8" t="n">
         <v>90580</v>
@@ -1504,8 +1496,16 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553815</v>
+        <v>553806</v>
       </c>
       <c r="R8" t="n">
-        <v>6634221</v>
+        <v>6634217</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120157354</v>
+        <v>120159215</v>
       </c>
       <c r="B9" t="n">
-        <v>8432</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1613,46 +1613,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553723</v>
+        <v>553741</v>
       </c>
       <c r="R9" t="n">
-        <v>6634334</v>
+        <v>6634339</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1681,7 +1683,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1691,7 +1693,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,28 +1708,28 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168936</v>
+        <v>120158850</v>
       </c>
       <c r="B10" t="n">
-        <v>8432</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1740,46 +1742,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553676</v>
+        <v>553726</v>
       </c>
       <c r="R10" t="n">
-        <v>6634439</v>
+        <v>6634313</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1806,9 +1810,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1823,28 +1837,28 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120169088</v>
+        <v>120157354</v>
       </c>
       <c r="B11" t="n">
-        <v>95478</v>
+        <v>8432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1853,39 +1867,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1926,9 +1937,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1954,17 +1975,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120158850</v>
+        <v>120168936</v>
       </c>
       <c r="B12" t="n">
-        <v>90545</v>
+        <v>8432</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1977,48 +1998,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553726</v>
+        <v>553676</v>
       </c>
       <c r="R12" t="n">
-        <v>6634313</v>
+        <v>6634439</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2045,19 +2064,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2072,28 +2081,28 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120159215</v>
+        <v>120163608</v>
       </c>
       <c r="B13" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2102,49 +2111,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553741</v>
+        <v>553722</v>
       </c>
       <c r="R13" t="n">
-        <v>6634339</v>
+        <v>6634626</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2176,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2186,7 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,17 +2226,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120163608</v>
+        <v>120169088</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2231,57 +2245,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553722</v>
+        <v>553723</v>
       </c>
       <c r="R14" t="n">
-        <v>6634626</v>
+        <v>6634334</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2308,19 +2318,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2335,18 +2335,18 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120156458</v>
+        <v>120168703</v>
       </c>
       <c r="B16" t="n">
-        <v>5169</v>
+        <v>105032</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2495,32 +2495,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2528,17 +2535,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553814</v>
+        <v>553705</v>
       </c>
       <c r="R16" t="n">
-        <v>6634170</v>
+        <v>6634586</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2565,24 +2572,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2608,17 +2600,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120193653</v>
+        <v>120156458</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2627,43 +2619,36 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2671,17 +2656,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lefelingen, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553699</v>
+        <v>553814</v>
       </c>
       <c r="R17" t="n">
-        <v>6634610</v>
+        <v>6634170</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2710,7 +2695,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2720,7 +2705,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,17 +2736,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168703</v>
+        <v>120193653</v>
       </c>
       <c r="B18" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2765,25 +2755,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2798,7 +2788,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2809,14 +2799,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lefelingen, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553705</v>
+        <v>553699</v>
       </c>
       <c r="R18" t="n">
-        <v>6634586</v>
+        <v>6634610</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2846,9 +2836,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120156999</v>
+        <v>120164833</v>
       </c>
       <c r="B20" t="n">
         <v>57473</v>
@@ -3053,17 +3053,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553742</v>
+        <v>553695</v>
       </c>
       <c r="R20" t="n">
-        <v>6634218</v>
+        <v>6634564</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3127,17 +3127,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120156618</v>
+        <v>120157172</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3150,45 +3150,49 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553801</v>
+        <v>553747</v>
       </c>
       <c r="R21" t="n">
-        <v>6634191</v>
+        <v>6634278</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3217,7 +3221,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3227,12 +3231,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska spår av födosök på gran</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3246,28 +3245,28 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120164833</v>
+        <v>120156618</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3280,49 +3279,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553695</v>
+        <v>553801</v>
       </c>
       <c r="R22" t="n">
-        <v>6634564</v>
+        <v>6634191</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3351,7 +3346,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3361,7 +3356,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3375,28 +3375,28 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120156648</v>
+        <v>120156999</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3409,21 +3409,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3435,7 +3435,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3445,13 +3445,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>553796</v>
+        <v>553742</v>
       </c>
       <c r="R23" t="n">
-        <v>6634191</v>
+        <v>6634218</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3522,10 +3522,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120157172</v>
+        <v>120156648</v>
       </c>
       <c r="B24" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3538,21 +3538,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3564,7 +3564,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3574,13 +3574,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553747</v>
+        <v>553796</v>
       </c>
       <c r="R24" t="n">
-        <v>6634278</v>
+        <v>6634191</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935427</v>
+        <v>119935492</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553848</v>
+        <v>553819</v>
       </c>
       <c r="R2" t="n">
-        <v>6634240</v>
+        <v>6634249</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -807,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119935357</v>
+        <v>119935597</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,51 +813,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553761</v>
+        <v>553806</v>
       </c>
       <c r="R3" t="n">
-        <v>6634190</v>
+        <v>6634217</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -943,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935492</v>
+        <v>119935446</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,30 +947,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -986,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553819</v>
+        <v>553835</v>
       </c>
       <c r="R4" t="n">
-        <v>6634249</v>
+        <v>6634247</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1069,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119931736</v>
+        <v>119935357</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,44 +1079,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553816</v>
+        <v>553761</v>
       </c>
       <c r="R5" t="n">
-        <v>6634237</v>
+        <v>6634190</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1145,19 +1153,9 @@
           <t>2024-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,14 +1196,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935520</v>
+        <v>119931736</v>
       </c>
       <c r="B6" t="n">
         <v>90580</v>
@@ -1248,13 +1246,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553815</v>
+        <v>553816</v>
       </c>
       <c r="R6" t="n">
-        <v>6634221</v>
+        <v>6634237</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,9 +1279,19 @@
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1324,17 +1332,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935446</v>
+        <v>119935520</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1343,36 +1351,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1380,10 +1382,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553835</v>
+        <v>553815</v>
       </c>
       <c r="R7" t="n">
-        <v>6634247</v>
+        <v>6634221</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1463,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935597</v>
+        <v>119935427</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1475,38 +1477,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553806</v>
+        <v>553848</v>
       </c>
       <c r="R8" t="n">
-        <v>6634217</v>
+        <v>6634240</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120159215</v>
+        <v>120157354</v>
       </c>
       <c r="B9" t="n">
-        <v>90545</v>
+        <v>8432</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1613,48 +1613,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553741</v>
+        <v>553723</v>
       </c>
       <c r="R9" t="n">
-        <v>6634339</v>
+        <v>6634334</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1683,7 +1681,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1693,7 +1691,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1708,25 +1706,25 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120158850</v>
+        <v>120159215</v>
       </c>
       <c r="B10" t="n">
         <v>90545</v>
@@ -1777,10 +1775,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553726</v>
+        <v>553741</v>
       </c>
       <c r="R10" t="n">
-        <v>6634313</v>
+        <v>6634339</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1812,7 +1810,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1822,7 +1820,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1855,10 +1853,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120157354</v>
+        <v>120163608</v>
       </c>
       <c r="B11" t="n">
-        <v>8432</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1867,50 +1865,57 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553723</v>
+        <v>553722</v>
       </c>
       <c r="R11" t="n">
-        <v>6634334</v>
+        <v>6634626</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1939,7 +1944,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,7 +1954,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1964,28 +1969,28 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168936</v>
+        <v>120169088</v>
       </c>
       <c r="B12" t="n">
-        <v>8432</v>
+        <v>95478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1994,36 +1999,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2031,10 +2039,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553676</v>
+        <v>553723</v>
       </c>
       <c r="R12" t="n">
-        <v>6634439</v>
+        <v>6634334</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2092,17 +2100,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120163608</v>
+        <v>120158850</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2111,54 +2119,49 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553722</v>
+        <v>553726</v>
       </c>
       <c r="R13" t="n">
-        <v>6634626</v>
+        <v>6634313</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2190,7 +2193,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2203,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2226,17 +2229,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120169088</v>
+        <v>120169031</v>
       </c>
       <c r="B14" t="n">
-        <v>95478</v>
+        <v>90545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2245,39 +2248,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2285,10 +2279,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553723</v>
+        <v>553676</v>
       </c>
       <c r="R14" t="n">
-        <v>6634334</v>
+        <v>6634439</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2338,6 +2332,21 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
@@ -2346,17 +2355,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120169031</v>
+        <v>120168936</v>
       </c>
       <c r="B15" t="n">
-        <v>90545</v>
+        <v>8432</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2369,26 +2378,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2447,21 +2462,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120156458</v>
+        <v>120193653</v>
       </c>
       <c r="B17" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2619,36 +2619,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2656,17 +2663,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lefelingen, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553814</v>
+        <v>553699</v>
       </c>
       <c r="R17" t="n">
-        <v>6634170</v>
+        <v>6634610</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2695,7 +2702,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2705,12 +2712,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2736,14 +2738,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120193653</v>
+        <v>119935336</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2778,7 +2780,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2792,24 +2794,20 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lefelingen, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553699</v>
+        <v>553767</v>
       </c>
       <c r="R18" t="n">
-        <v>6634610</v>
+        <v>6634197</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2833,22 +2831,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2874,17 +2862,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119935336</v>
+        <v>120156458</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2893,57 +2881,54 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553767</v>
+        <v>553814</v>
       </c>
       <c r="R19" t="n">
-        <v>6634197</v>
+        <v>6634170</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2967,12 +2952,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3005,7 +3005,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120164833</v>
+        <v>120157172</v>
       </c>
       <c r="B20" t="n">
         <v>57473</v>
@@ -3053,14 +3053,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553695</v>
+        <v>553747</v>
       </c>
       <c r="R20" t="n">
-        <v>6634564</v>
+        <v>6634278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120157172</v>
+        <v>120164833</v>
       </c>
       <c r="B21" t="n">
         <v>57473</v>
@@ -3182,14 +3182,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553747</v>
+        <v>553695</v>
       </c>
       <c r="R21" t="n">
-        <v>6634278</v>
+        <v>6634564</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3256,17 +3256,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120156618</v>
+        <v>120156999</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3279,45 +3279,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553801</v>
+        <v>553742</v>
       </c>
       <c r="R22" t="n">
-        <v>6634191</v>
+        <v>6634218</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3346,7 +3350,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3356,12 +3360,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska spår av födosök på gran</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3375,28 +3374,28 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Leif Tallberg, Bengt Eriksson, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120156999</v>
+        <v>120156618</v>
       </c>
       <c r="B23" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3409,49 +3408,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>553742</v>
+        <v>553801</v>
       </c>
       <c r="R23" t="n">
-        <v>6634218</v>
+        <v>6634191</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3480,7 +3475,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3490,7 +3485,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3504,18 +3504,18 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935492</v>
+        <v>119935427</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553819</v>
+        <v>553848</v>
       </c>
       <c r="R2" t="n">
-        <v>6634249</v>
+        <v>6634240</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -801,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119935597</v>
+        <v>119935446</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,38 +819,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553806</v>
+        <v>553835</v>
       </c>
       <c r="R3" t="n">
-        <v>6634217</v>
+        <v>6634247</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -935,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935446</v>
+        <v>119935597</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,36 +951,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -984,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553835</v>
+        <v>553806</v>
       </c>
       <c r="R4" t="n">
-        <v>6634247</v>
+        <v>6634217</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1067,10 +1073,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935357</v>
+        <v>119935520</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,51 +1085,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553761</v>
+        <v>553815</v>
       </c>
       <c r="R5" t="n">
-        <v>6634190</v>
+        <v>6634221</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1203,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119931736</v>
+        <v>119935492</v>
       </c>
       <c r="B6" t="n">
         <v>90580</v>
@@ -1246,13 +1242,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553816</v>
+        <v>553819</v>
       </c>
       <c r="R6" t="n">
-        <v>6634237</v>
+        <v>6634249</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1279,19 +1275,9 @@
           <t>2024-09-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1332,14 +1318,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935520</v>
+        <v>119931736</v>
       </c>
       <c r="B7" t="n">
         <v>90580</v>
@@ -1382,13 +1368,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553815</v>
+        <v>553816</v>
       </c>
       <c r="R7" t="n">
-        <v>6634221</v>
+        <v>6634237</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1415,9 +1401,19 @@
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1458,14 +1454,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935427</v>
+        <v>119935357</v>
       </c>
       <c r="B8" t="n">
         <v>5169</v>
@@ -1507,17 +1503,21 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553848</v>
+        <v>553761</v>
       </c>
       <c r="R8" t="n">
-        <v>6634240</v>
+        <v>6634190</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120157354</v>
+        <v>120169088</v>
       </c>
       <c r="B9" t="n">
-        <v>8432</v>
+        <v>95478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1609,36 +1609,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1679,19 +1682,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1717,14 +1710,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120159215</v>
+        <v>120169031</v>
       </c>
       <c r="B10" t="n">
         <v>90545</v>
@@ -1757,31 +1750,23 @@
           <t>(Schwein.) Murrill</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553741</v>
+        <v>553676</v>
       </c>
       <c r="R10" t="n">
-        <v>6634339</v>
+        <v>6634439</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1808,19 +1793,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1835,28 +1810,43 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120163608</v>
+        <v>120157354</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>8432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1865,57 +1855,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553722</v>
+        <v>553723</v>
       </c>
       <c r="R11" t="n">
-        <v>6634626</v>
+        <v>6634334</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1944,7 +1927,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1954,7 +1937,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1969,28 +1952,28 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120169088</v>
+        <v>120168936</v>
       </c>
       <c r="B12" t="n">
-        <v>95478</v>
+        <v>8432</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1999,39 +1982,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2039,10 +2019,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553723</v>
+        <v>553676</v>
       </c>
       <c r="R12" t="n">
-        <v>6634334</v>
+        <v>6634439</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2100,17 +2080,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120158850</v>
+        <v>120163608</v>
       </c>
       <c r="B13" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2119,49 +2099,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553726</v>
+        <v>553722</v>
       </c>
       <c r="R13" t="n">
-        <v>6634313</v>
+        <v>6634626</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2193,7 +2178,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2203,7 +2188,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2229,14 +2214,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120169031</v>
+        <v>120158850</v>
       </c>
       <c r="B14" t="n">
         <v>90545</v>
@@ -2269,23 +2254,31 @@
           <t>(Schwein.) Murrill</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553676</v>
+        <v>553726</v>
       </c>
       <c r="R14" t="n">
-        <v>6634439</v>
+        <v>6634313</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2312,9 +2305,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2329,43 +2332,28 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168936</v>
+        <v>120159215</v>
       </c>
       <c r="B15" t="n">
-        <v>8432</v>
+        <v>90545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2378,46 +2366,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553676</v>
+        <v>553741</v>
       </c>
       <c r="R15" t="n">
-        <v>6634439</v>
+        <v>6634339</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2444,9 +2434,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2461,28 +2461,28 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168703</v>
+        <v>120156458</v>
       </c>
       <c r="B16" t="n">
-        <v>105032</v>
+        <v>5169</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2495,39 +2495,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2535,17 +2528,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553705</v>
+        <v>553814</v>
       </c>
       <c r="R16" t="n">
-        <v>6634586</v>
+        <v>6634170</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2572,9 +2565,24 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2600,7 +2608,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2869,10 +2877,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120156458</v>
+        <v>120168703</v>
       </c>
       <c r="B19" t="n">
-        <v>5169</v>
+        <v>105032</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2885,32 +2893,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2918,17 +2933,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553814</v>
+        <v>553705</v>
       </c>
       <c r="R19" t="n">
-        <v>6634170</v>
+        <v>6634586</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2955,24 +2970,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120156999</v>
+        <v>120156618</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3279,49 +3279,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553742</v>
+        <v>553801</v>
       </c>
       <c r="R22" t="n">
-        <v>6634218</v>
+        <v>6634191</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3350,7 +3346,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3360,7 +3356,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3374,25 +3375,25 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Leif Tallberg, Bengt Eriksson, Pia Hagfors, Sören Larsson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120156618</v>
+        <v>120156648</v>
       </c>
       <c r="B23" t="n">
         <v>57336</v>
@@ -3425,7 +3426,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -3436,11 +3441,11 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>553801</v>
+        <v>553796</v>
       </c>
       <c r="R23" t="n">
         <v>6634191</v>
@@ -3475,7 +3480,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3485,12 +3490,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska spår av födosök på gran</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3504,28 +3504,28 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120156648</v>
+        <v>120156999</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3538,21 +3538,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3564,7 +3564,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3574,13 +3574,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553796</v>
+        <v>553742</v>
       </c>
       <c r="R24" t="n">
-        <v>6634191</v>
+        <v>6634218</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119935446</v>
+        <v>119935357</v>
       </c>
       <c r="B3" t="n">
         <v>5169</v>
@@ -849,17 +849,21 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553835</v>
+        <v>553761</v>
       </c>
       <c r="R3" t="n">
-        <v>6634247</v>
+        <v>6634190</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -939,7 +943,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935597</v>
+        <v>119931736</v>
       </c>
       <c r="B4" t="n">
         <v>90580</v>
@@ -972,16 +976,8 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -990,13 +986,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553806</v>
+        <v>553816</v>
       </c>
       <c r="R4" t="n">
-        <v>6634217</v>
+        <v>6634237</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1023,9 +1019,19 @@
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1066,14 +1072,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935520</v>
+        <v>119935597</v>
       </c>
       <c r="B5" t="n">
         <v>90580</v>
@@ -1106,8 +1112,16 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1116,10 +1130,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553815</v>
+        <v>553806</v>
       </c>
       <c r="R5" t="n">
-        <v>6634221</v>
+        <v>6634217</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1325,10 +1339,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119931736</v>
+        <v>119935446</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,30 +1351,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1368,13 +1388,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553816</v>
+        <v>553835</v>
       </c>
       <c r="R7" t="n">
-        <v>6634237</v>
+        <v>6634247</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1401,19 +1421,9 @@
           <t>2024-09-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,17 +1464,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935357</v>
+        <v>119935520</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1473,51 +1483,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553761</v>
+        <v>553815</v>
       </c>
       <c r="R8" t="n">
-        <v>6634190</v>
+        <v>6634221</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120169088</v>
+        <v>120157354</v>
       </c>
       <c r="B9" t="n">
-        <v>95478</v>
+        <v>8432</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1609,39 +1609,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1682,9 +1679,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,17 +1717,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120169031</v>
+        <v>120168936</v>
       </c>
       <c r="B10" t="n">
-        <v>90545</v>
+        <v>8432</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1733,26 +1740,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1811,21 +1824,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1843,10 +1841,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120157354</v>
+        <v>120169088</v>
       </c>
       <c r="B11" t="n">
-        <v>8432</v>
+        <v>95478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1855,36 +1853,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1925,19 +1926,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1963,17 +1954,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168936</v>
+        <v>120169031</v>
       </c>
       <c r="B12" t="n">
-        <v>8432</v>
+        <v>90545</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1986,32 +1977,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2070,6 +2055,21 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120163608</v>
+        <v>120159215</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2099,54 +2099,49 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553722</v>
+        <v>553741</v>
       </c>
       <c r="R13" t="n">
-        <v>6634626</v>
+        <v>6634339</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2178,7 +2173,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2188,7 +2183,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2214,7 +2209,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2350,10 +2345,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120159215</v>
+        <v>120163608</v>
       </c>
       <c r="B15" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2362,49 +2357,54 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553741</v>
+        <v>553722</v>
       </c>
       <c r="R15" t="n">
-        <v>6634339</v>
+        <v>6634626</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120156458</v>
+        <v>120193653</v>
       </c>
       <c r="B16" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2491,36 +2491,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2528,17 +2535,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lefelingen, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553814</v>
+        <v>553699</v>
       </c>
       <c r="R16" t="n">
-        <v>6634170</v>
+        <v>6634610</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2567,7 +2574,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2577,12 +2584,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2608,17 +2610,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120193653</v>
+        <v>120168703</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2627,25 +2629,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2660,7 +2662,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2671,14 +2673,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lefelingen, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553699</v>
+        <v>553705</v>
       </c>
       <c r="R17" t="n">
-        <v>6634610</v>
+        <v>6634586</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2708,19 +2710,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,17 +2738,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119935336</v>
+        <v>120156458</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2765,57 +2757,54 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553767</v>
+        <v>553814</v>
       </c>
       <c r="R18" t="n">
-        <v>6634197</v>
+        <v>6634170</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2839,12 +2828,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2877,10 +2881,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168703</v>
+        <v>119935336</v>
       </c>
       <c r="B19" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2889,30 +2893,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2922,28 +2926,24 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553705</v>
+        <v>553767</v>
       </c>
       <c r="R19" t="n">
-        <v>6634586</v>
+        <v>6634197</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2998,14 +2998,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120157172</v>
+        <v>120156999</v>
       </c>
       <c r="B20" t="n">
         <v>57473</v>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553747</v>
+        <v>553742</v>
       </c>
       <c r="R20" t="n">
-        <v>6634278</v>
+        <v>6634218</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3127,17 +3127,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Seppo Ormiskangas, Leif Tallberg, Bengt Eriksson, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120164833</v>
+        <v>120156618</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3150,49 +3150,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553695</v>
+        <v>553801</v>
       </c>
       <c r="R21" t="n">
-        <v>6634564</v>
+        <v>6634191</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3221,7 +3217,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3231,7 +3227,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3245,28 +3246,28 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120156618</v>
+        <v>120157172</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3279,45 +3280,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553801</v>
+        <v>553747</v>
       </c>
       <c r="R22" t="n">
-        <v>6634191</v>
+        <v>6634278</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3346,7 +3351,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3356,12 +3361,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska spår av födosök på gran</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3375,18 +3375,18 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3515,14 +3515,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Seppo Ormiskangas, Leif Tallberg, Bengt Eriksson, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120156999</v>
+        <v>120164833</v>
       </c>
       <c r="B24" t="n">
         <v>57473</v>
@@ -3570,17 +3570,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553742</v>
+        <v>553695</v>
       </c>
       <c r="R24" t="n">
-        <v>6634218</v>
+        <v>6634564</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935427</v>
+        <v>119935446</v>
       </c>
       <c r="B2" t="n">
         <v>5169</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553848</v>
+        <v>553835</v>
       </c>
       <c r="R2" t="n">
-        <v>6634240</v>
+        <v>6634247</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119931736</v>
+        <v>119935597</v>
       </c>
       <c r="B4" t="n">
         <v>90580</v>
@@ -976,8 +976,16 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -986,13 +994,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553816</v>
+        <v>553806</v>
       </c>
       <c r="R4" t="n">
-        <v>6634237</v>
+        <v>6634217</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,19 +1027,9 @@
           <t>2024-09-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1072,14 +1070,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935597</v>
+        <v>119931736</v>
       </c>
       <c r="B5" t="n">
         <v>90580</v>
@@ -1112,16 +1110,8 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1130,13 +1120,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553806</v>
+        <v>553816</v>
       </c>
       <c r="R5" t="n">
-        <v>6634217</v>
+        <v>6634237</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1163,9 +1153,19 @@
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1206,14 +1206,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935492</v>
+        <v>119935520</v>
       </c>
       <c r="B6" t="n">
         <v>90580</v>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553819</v>
+        <v>553815</v>
       </c>
       <c r="R6" t="n">
-        <v>6634249</v>
+        <v>6634221</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935446</v>
+        <v>119935492</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,36 +1351,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1388,10 +1382,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553835</v>
+        <v>553819</v>
       </c>
       <c r="R7" t="n">
-        <v>6634247</v>
+        <v>6634249</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1471,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935520</v>
+        <v>119935427</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,30 +1477,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553815</v>
+        <v>553848</v>
       </c>
       <c r="R8" t="n">
-        <v>6634221</v>
+        <v>6634240</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120157354</v>
+        <v>120158850</v>
       </c>
       <c r="B9" t="n">
-        <v>8432</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1613,46 +1613,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553723</v>
+        <v>553726</v>
       </c>
       <c r="R9" t="n">
-        <v>6634334</v>
+        <v>6634313</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1681,7 +1683,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1691,7 +1693,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,28 +1708,28 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168936</v>
+        <v>120169088</v>
       </c>
       <c r="B10" t="n">
-        <v>8432</v>
+        <v>95478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,36 +1738,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1773,10 +1778,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553676</v>
+        <v>553723</v>
       </c>
       <c r="R10" t="n">
-        <v>6634439</v>
+        <v>6634334</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1834,17 +1839,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120169088</v>
+        <v>120157354</v>
       </c>
       <c r="B11" t="n">
-        <v>95478</v>
+        <v>8432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1853,39 +1858,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1926,9 +1928,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1954,7 +1966,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2216,10 +2228,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120158850</v>
+        <v>120168936</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>8432</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2232,48 +2244,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553726</v>
+        <v>553676</v>
       </c>
       <c r="R14" t="n">
-        <v>6634313</v>
+        <v>6634439</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2300,19 +2310,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2327,18 +2327,18 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168703</v>
+        <v>120156458</v>
       </c>
       <c r="B17" t="n">
-        <v>105032</v>
+        <v>5169</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2633,39 +2633,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2673,17 +2666,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553705</v>
+        <v>553814</v>
       </c>
       <c r="R17" t="n">
-        <v>6634586</v>
+        <v>6634170</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2710,9 +2703,24 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2738,17 +2746,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120156458</v>
+        <v>119935336</v>
       </c>
       <c r="B18" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2757,54 +2765,57 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553814</v>
+        <v>553767</v>
       </c>
       <c r="R18" t="n">
-        <v>6634170</v>
+        <v>6634197</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2828,27 +2839,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2881,10 +2877,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119935336</v>
+        <v>120168703</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2893,30 +2889,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2926,24 +2922,28 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553767</v>
+        <v>553705</v>
       </c>
       <c r="R19" t="n">
-        <v>6634197</v>
+        <v>6634586</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2998,14 +2998,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120156999</v>
+        <v>120164833</v>
       </c>
       <c r="B20" t="n">
         <v>57473</v>
@@ -3053,17 +3053,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553742</v>
+        <v>553695</v>
       </c>
       <c r="R20" t="n">
-        <v>6634218</v>
+        <v>6634564</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Leif Tallberg, Bengt Eriksson, Pia Hagfors, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120157172</v>
+        <v>120156999</v>
       </c>
       <c r="B22" t="n">
         <v>57473</v>
@@ -3316,13 +3316,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553747</v>
+        <v>553742</v>
       </c>
       <c r="R22" t="n">
-        <v>6634278</v>
+        <v>6634218</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3515,14 +3515,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Leif Tallberg, Bengt Eriksson, Pia Hagfors, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120164833</v>
+        <v>120157172</v>
       </c>
       <c r="B24" t="n">
         <v>57473</v>
@@ -3570,14 +3570,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553695</v>
+        <v>553747</v>
       </c>
       <c r="R24" t="n">
-        <v>6634564</v>
+        <v>6634278</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -3773,7 +3773,7 @@
         <v>121121628</v>
       </c>
       <c r="B26" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -3773,7 +3773,7 @@
         <v>121121628</v>
       </c>
       <c r="B26" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -3773,7 +3773,7 @@
         <v>121121628</v>
       </c>
       <c r="B26" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -3773,7 +3773,7 @@
         <v>121121628</v>
       </c>
       <c r="B26" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935446</v>
+        <v>120169088</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553835</v>
+        <v>553723</v>
       </c>
       <c r="R2" t="n">
-        <v>6634247</v>
+        <v>6634334</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,21 +775,6 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -800,73 +783,58 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119935357</v>
+        <v>119931736</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553761</v>
+        <v>553816</v>
       </c>
       <c r="R3" t="n">
-        <v>6634190</v>
+        <v>6634237</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,9 +861,19 @@
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,22 +914,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935597</v>
+        <v>119935492</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,16 +949,8 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -994,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553806</v>
+        <v>553819</v>
       </c>
       <c r="R4" t="n">
-        <v>6634217</v>
+        <v>6634249</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1077,15 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119931736</v>
+        <v>119935520</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553816</v>
+        <v>553815</v>
       </c>
       <c r="R5" t="n">
-        <v>6634237</v>
+        <v>6634221</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,19 +1113,9 @@
           <t>2024-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1206,22 +1156,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935520</v>
+        <v>119935597</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,8 +1191,16 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1256,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553815</v>
+        <v>553806</v>
       </c>
       <c r="R6" t="n">
-        <v>6634221</v>
+        <v>6634217</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1339,56 +1292,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935492</v>
+        <v>120319498</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Tordyvelskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553819</v>
+        <v>553728</v>
       </c>
       <c r="R7" t="n">
-        <v>6634249</v>
+        <v>6634325</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1412,12 +1368,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På grov granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1430,50 +1391,25 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935427</v>
+        <v>120158850</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,43 +1417,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553848</v>
+        <v>553726</v>
       </c>
       <c r="R8" t="n">
-        <v>6634240</v>
+        <v>6634313</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1544,12 +1482,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1564,99 +1512,74 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120163608</v>
+        <v>120159215</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553722</v>
+        <v>553741</v>
       </c>
       <c r="R9" t="n">
-        <v>6634626</v>
+        <v>6634339</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1688,7 +1611,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1698,7 +1621,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1724,22 +1647,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168936</v>
+        <v>120169031</v>
       </c>
       <c r="B10" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,32 +1665,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1831,6 +1743,21 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1848,15 +1775,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120158850</v>
+        <v>120156618</v>
       </c>
       <c r="B11" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1864,48 +1786,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553726</v>
+        <v>553801</v>
       </c>
       <c r="R11" t="n">
-        <v>6634313</v>
+        <v>6634191</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1934,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1944,7 +1863,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1953,86 +1877,80 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120169088</v>
+        <v>120156648</v>
       </c>
       <c r="B12" t="n">
-        <v>95478</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553723</v>
+        <v>553796</v>
       </c>
       <c r="R12" t="n">
-        <v>6634334</v>
+        <v>6634191</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2062,50 +1980,54 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas, Leif Tallberg, Bengt Eriksson, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120159215</v>
+        <v>119935386</v>
       </c>
       <c r="B13" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,45 +2035,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553741</v>
+        <v>553868</v>
       </c>
       <c r="R13" t="n">
-        <v>6634339</v>
+        <v>6634240</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2178,22 +2105,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:13</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:13</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2202,39 +2119,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson, Leif Tallberg, Bengt Eriksson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120169031</v>
+        <v>120156920</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2242,37 +2153,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Li Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553676</v>
+        <v>553729</v>
       </c>
       <c r="R14" t="n">
-        <v>6634439</v>
+        <v>6634204</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2302,39 +2226,38 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2345,22 +2268,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120157354</v>
+        <v>119935357</v>
       </c>
       <c r="B15" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,21 +2286,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2394,20 +2312,24 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553723</v>
+        <v>553761</v>
       </c>
       <c r="R15" t="n">
-        <v>6634334</v>
+        <v>6634190</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2431,22 +2353,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2462,6 +2374,21 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2479,55 +2406,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119935336</v>
+        <v>119935427</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2535,13 +2450,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553767</v>
+        <v>553848</v>
       </c>
       <c r="R16" t="n">
-        <v>6634197</v>
+        <v>6634240</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2586,6 +2501,21 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2603,15 +2533,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168703</v>
+        <v>119935446</v>
       </c>
       <c r="B17" t="n">
-        <v>105032</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2619,54 +2544,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553705</v>
+        <v>553835</v>
       </c>
       <c r="R17" t="n">
-        <v>6634586</v>
+        <v>6634247</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2693,12 +2607,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2716,6 +2630,21 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
@@ -2724,7 +2653,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2734,12 +2663,7 @@
         <v>120156458</v>
       </c>
       <c r="B18" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2867,37 +2791,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120193653</v>
+        <v>120156999</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2905,35 +2824,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lefelingen, Virsbo, Vstm</t>
+          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553699</v>
+        <v>553742</v>
       </c>
       <c r="R19" t="n">
-        <v>6634610</v>
+        <v>6634218</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2962,7 +2873,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2972,7 +2883,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2981,39 +2892,33 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120156648</v>
+        <v>120157172</v>
       </c>
       <c r="B20" t="n">
-        <v>57349</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3021,21 +2926,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3047,7 +2952,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3057,13 +2962,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553796</v>
+        <v>553747</v>
       </c>
       <c r="R20" t="n">
-        <v>6634191</v>
+        <v>6634278</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3092,7 +2997,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3102,7 +3007,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3134,15 +3039,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120156618</v>
+        <v>120164833</v>
       </c>
       <c r="B21" t="n">
-        <v>57349</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3150,45 +3050,49 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilla Avlången, Virsbo, Vstm, Lilla Avlången, Virsbo, Vstm, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553801</v>
+        <v>553695</v>
       </c>
       <c r="R21" t="n">
-        <v>6634191</v>
+        <v>6634564</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3217,7 +3121,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3227,12 +3131,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska spår av födosök på gran</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3246,83 +3145,75 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120156999</v>
+        <v>120157354</v>
       </c>
       <c r="B22" t="n">
-        <v>57486</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553742</v>
+        <v>553723</v>
       </c>
       <c r="R22" t="n">
-        <v>6634218</v>
+        <v>6634334</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3351,7 +3242,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3361,7 +3252,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3370,88 +3261,81 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120157172</v>
+        <v>120168936</v>
       </c>
       <c r="B23" t="n">
-        <v>57486</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Tordyvelskogen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>553747</v>
+        <v>553676</v>
       </c>
       <c r="R23" t="n">
-        <v>6634278</v>
+        <v>6634439</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3478,106 +3362,96 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors, Bengt Eriksson, Leif Tallberg</t>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120164833</v>
+        <v>119935336</v>
       </c>
       <c r="B24" t="n">
-        <v>57486</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lefelingen, Lefelingen, Vstm</t>
+          <t>Lilla Avlången, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553695</v>
+        <v>553767</v>
       </c>
       <c r="R24" t="n">
-        <v>6634564</v>
+        <v>6634197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3604,22 +3478,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3628,60 +3492,56 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120319498</v>
+        <v>120163608</v>
       </c>
       <c r="B25" t="n">
-        <v>90650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3691,24 +3551,29 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tordyvelskogen, Ramnäs sn, Vstm</t>
+          <t>Lefelingen, Lefelingen, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>553728</v>
+        <v>553722</v>
       </c>
       <c r="R25" t="n">
-        <v>6634325</v>
+        <v>6634626</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3735,14 +3600,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På grov granlåga</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3755,30 +3625,30 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121121628</v>
+        <v>120193653</v>
       </c>
       <c r="B26" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3819,20 +3689,24 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lefelingen 3 (knärot) , Vstm</t>
+          <t>Lefelingen, Virsbo, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553722</v>
+        <v>553699</v>
       </c>
       <c r="R26" t="n">
-        <v>6634627</v>
+        <v>6634610</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3854,19 +3728,24 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>U-Sur-0779</t>
-        </is>
-      </c>
       <c r="Y26" t="inlineStr">
         <is>
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3879,27 +3758,397 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>häll- och blockskog</t>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120204221</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lefelingen, Virsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>553728</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6634251</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Sören Larsson, Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121121628</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lefelingen 3 (knärot) , Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>553722</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6634627</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>U-Sur-0779</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>häll- och blockskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Bo Eriksson</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Seppo Ormiskangas, Sören Larsson, Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
+      <c r="AY28" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120168703</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lilla Avlången, Virsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>553705</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6634586</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Seppo Ormiskangas, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34040-2024 artfynd.xlsx
+++ b/artfynd/A 34040-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120169088</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119931736</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,6 +1054,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119935492</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1160,6 +1180,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119935520</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1289,6 +1314,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119935597</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1403,6 +1433,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120319498</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1527,6 +1562,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120158850</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1651,6 +1691,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120159215</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1772,6 +1817,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120169031</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1897,6 +1947,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120156618</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2021,6 +2076,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120156648</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2139,6 +2199,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119935386</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2272,6 +2337,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120156920</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2403,6 +2473,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119935357</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2530,6 +2605,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119935427</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2657,6 +2737,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119935446</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2788,6 +2873,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120156458</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2912,6 +3002,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120156999</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3036,6 +3131,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120157172</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3160,6 +3260,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120164833</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3282,6 +3387,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120157354</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3394,6 +3504,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120168936</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3513,6 +3628,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119935336</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3642,6 +3762,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120163608</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3775,6 +3900,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120193653</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3898,6 +4028,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120204221</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4026,6 +4161,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121121628</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4149,8 +4289,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120168703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>